--- a/results_release.xlsx
+++ b/results_release.xlsx
@@ -1,31 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SHU\code\xiaji2\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F24CC49-964B-4B6F-8737-50D45D24F530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{4B30CB73-B72B-4AC1-AE04-B5709F744D2F}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="results_release" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="results_release" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="38">
   <si>
     <t>Mon Jul 13 10:15:41 PM CST 2026</t>
   </si>
   <si>
+    <t>Sun Dec 31 1899 05:52:23 GMT+0736 (香港标准时间)</t>
+  </si>
+  <si>
+    <t>*比较次数与赋值次数顺序与排序顺序一致</t>
+  </si>
+  <si>
+    <t>数据类型：i整数，d双精度浮点</t>
+  </si>
+  <si>
+    <t>*-1表示因时间过长或堆栈溢出故停止</t>
+  </si>
+  <si>
     <t>数据类型: i (完全逆序)</t>
+  </si>
+  <si>
+    <t>耗时（秒）</t>
   </si>
   <si>
     <t>冒泡排序</t>
@@ -44,6 +50,15 @@
   </si>
   <si>
     <t>桶排序</t>
+  </si>
+  <si>
+    <t>比较次数（次）</t>
+  </si>
+  <si>
+    <t>赋值次数（次）</t>
+  </si>
+  <si>
+    <t>是否正确</t>
   </si>
   <si>
     <t>正确</t>
@@ -70,418 +85,79 @@
     <t>数据类型: d (正态分布)</t>
   </si>
   <si>
+    <t>*以下为使用各种排序算法对结构体排序</t>
+  </si>
+  <si>
     <t>原始数据分布: 正态分布, 数据类型 = 5Score</t>
+  </si>
+  <si>
+    <t>比较次数</t>
+  </si>
+  <si>
+    <t>赋值次数</t>
   </si>
   <si>
     <t>*** 多种不同存储方式的C-字符串数组的排序 ***</t>
   </si>
   <si>
-    <t>原始数据: enter, number, size, begin, of, cat, case, program, certain, a, cake, side</t>
+    <t>type</t>
   </si>
   <si>
-    <t>数组指针排序结果: a, begin, cake, case, cat, certain, enter, number, of, program, side, size</t>
+    <t>time</t>
   </si>
   <si>
-    <t>原始数据: enter, number, size, begin, of, cat, case, program, certain, an, cake, side</t>
+    <t>cmp_cnt</t>
   </si>
   <si>
-    <t>指针数组排序结果: an, begin, cake, case, cat, certain, enter, number, of, program, side, size</t>
+    <t>asn_cnt</t>
   </si>
   <si>
-    <t>指针数组排序结果: a, begin, cake, case, cat, certain, enter, number, of, program, side, size</t>
+    <t>StrA</t>
   </si>
   <si>
-    <t>比较次数</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>StrB</t>
   </si>
   <si>
-    <t>赋值次数</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>StrC</t>
   </si>
   <si>
-    <t>是否正确</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>StrD</t>
   </si>
   <si>
-    <t>*比较次数与赋值次数顺序与排序顺序一致</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据类型：i整数，d双精度浮点</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>*以下为对数组指针与指针数组差异的研究</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>耗时（秒）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>*以下为使用各种排序算法对结构体排序</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>比较次数（次）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>赋值次数（次）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>*-1表示因时间过长或堆栈溢出故停止</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+    <t>Sun Dec 31 1899 06:08:54 GMT+0736 (香港标准时间)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线 Light"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF2C3E50"/>
+      <sz val="12"/>
+      <name val="Noto Sans SC"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -489,293 +165,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -791,7 +195,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -801,44 +205,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -866,31 +270,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -918,23 +305,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -946,136 +316,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -1097,147 +511,146 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B89E0E4D-ADD4-4EC6-9FED-0B9A65946BB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y157"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.08203125" customWidth="1"/>
+    <col min="1" max="1" width="35.285714285714285" customWidth="1"/>
+    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
+    <col min="3" max="4" width="35.285714285714285" customWidth="1"/>
+    <col min="5" max="7" width="13.571428571428571" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="25" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>0.92755787037037041</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M5" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1024</v>
       </c>
       <c r="B6">
-        <v>2.5219999999999999E-3</v>
+        <v>0.002522</v>
       </c>
       <c r="C6">
-        <v>8.9700000000000001E-4</v>
+        <v>0.000897</v>
       </c>
       <c r="D6">
-        <v>2.4000000000000001E-5</v>
+        <v>0.000024</v>
       </c>
       <c r="E6">
-        <v>1.2899999999999999E-3</v>
+        <v>0.00129</v>
       </c>
       <c r="F6">
-        <v>4.8999999999999998E-5</v>
+        <v>0.000049</v>
       </c>
       <c r="G6">
-        <v>9.6000000000000002E-5</v>
+        <v>0.000096</v>
       </c>
       <c r="H6">
         <v>523776</v>
@@ -1276,45 +689,45 @@
         <v>1024</v>
       </c>
       <c r="T6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2048</v>
       </c>
       <c r="B7">
-        <v>1.0063000000000001E-2</v>
+        <v>0.010063</v>
       </c>
       <c r="C7">
-        <v>3.1050000000000001E-3</v>
+        <v>0.003105</v>
       </c>
       <c r="D7">
-        <v>3.6999999999999998E-5</v>
+        <v>0.000037</v>
       </c>
       <c r="E7">
-        <v>5.2350000000000001E-3</v>
+        <v>0.005235</v>
       </c>
       <c r="F7">
-        <v>1.0399999999999999E-4</v>
+        <v>0.000104</v>
       </c>
       <c r="G7">
-        <v>1.54E-4</v>
+        <v>0.000154</v>
       </c>
       <c r="H7">
         <v>2096128</v>
@@ -1353,45 +766,45 @@
         <v>2048</v>
       </c>
       <c r="T7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X7" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4096</v>
       </c>
       <c r="B8">
-        <v>3.9569E-2</v>
+        <v>0.039569</v>
       </c>
       <c r="C8">
-        <v>1.1795E-2</v>
+        <v>0.011795</v>
       </c>
       <c r="D8">
-        <v>8.6000000000000003E-5</v>
+        <v>0.000086</v>
       </c>
       <c r="E8">
-        <v>2.0702000000000002E-2</v>
+        <v>0.020702</v>
       </c>
       <c r="F8">
-        <v>2.5399999999999999E-4</v>
+        <v>0.000254</v>
       </c>
       <c r="G8">
-        <v>3.3300000000000002E-4</v>
+        <v>0.000333</v>
       </c>
       <c r="H8">
         <v>8386560</v>
@@ -1430,45 +843,45 @@
         <v>4096</v>
       </c>
       <c r="T8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8192</v>
       </c>
       <c r="B9">
-        <v>0.15936400000000001</v>
+        <v>0.159364</v>
       </c>
       <c r="C9">
-        <v>4.7487000000000001E-2</v>
+        <v>0.047487</v>
       </c>
       <c r="D9">
-        <v>1.6899999999999999E-4</v>
+        <v>0.000169</v>
       </c>
       <c r="E9">
-        <v>8.9020000000000002E-2</v>
+        <v>0.08902</v>
       </c>
       <c r="F9">
-        <v>5.1400000000000003E-4</v>
+        <v>0.000514</v>
       </c>
       <c r="G9">
-        <v>6.11E-4</v>
+        <v>0.000611</v>
       </c>
       <c r="H9">
         <v>33550336</v>
@@ -1507,45 +920,45 @@
         <v>8192</v>
       </c>
       <c r="T9" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U9" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V9" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W9" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X9" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>16384</v>
       </c>
       <c r="B10">
-        <v>0.63879600000000003</v>
+        <v>0.638796</v>
       </c>
       <c r="C10">
-        <v>0.18659899999999999</v>
+        <v>0.186599</v>
       </c>
       <c r="D10">
-        <v>3.3700000000000001E-4</v>
+        <v>0.000337</v>
       </c>
       <c r="E10">
-        <v>0.32839499999999999</v>
+        <v>0.328395</v>
       </c>
       <c r="F10">
-        <v>1.281E-3</v>
+        <v>0.001281</v>
       </c>
       <c r="G10">
-        <v>1.2459999999999999E-3</v>
+        <v>0.001246</v>
       </c>
       <c r="H10">
         <v>134209536</v>
@@ -1584,25 +997,25 @@
         <v>16384</v>
       </c>
       <c r="T10" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U10" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V10" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W10" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X10" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>32768</v>
       </c>
@@ -1610,7 +1023,7 @@
         <v>-1</v>
       </c>
       <c r="C11">
-        <v>0.75995100000000004</v>
+        <v>0.759951</v>
       </c>
       <c r="D11">
         <v>-1</v>
@@ -1619,10 +1032,10 @@
         <v>1.346314</v>
       </c>
       <c r="F11">
-        <v>2.4489999999999998E-3</v>
+        <v>0.002449</v>
       </c>
       <c r="G11">
-        <v>2.431E-3</v>
+        <v>0.002431</v>
       </c>
       <c r="H11">
         <v>-1</v>
@@ -1661,25 +1074,25 @@
         <v>32768</v>
       </c>
       <c r="T11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X11" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>65536</v>
       </c>
@@ -1687,19 +1100,19 @@
         <v>-1</v>
       </c>
       <c r="C12">
-        <v>2.9937559999999999</v>
+        <v>2.993756</v>
       </c>
       <c r="D12">
         <v>-1</v>
       </c>
       <c r="E12">
-        <v>5.3034970000000001</v>
+        <v>5.303497</v>
       </c>
       <c r="F12">
-        <v>5.2709999999999996E-3</v>
+        <v>0.005271</v>
       </c>
       <c r="G12">
-        <v>5.64E-3</v>
+        <v>0.00564</v>
       </c>
       <c r="H12">
         <v>-1</v>
@@ -1738,25 +1151,25 @@
         <v>65536</v>
       </c>
       <c r="T12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X12" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>131072</v>
       </c>
@@ -1770,13 +1183,13 @@
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>21.115580000000001</v>
+        <v>21.11558</v>
       </c>
       <c r="F13">
-        <v>1.2111E-2</v>
+        <v>0.012111</v>
       </c>
       <c r="G13">
-        <v>1.1497E-2</v>
+        <v>0.011497</v>
       </c>
       <c r="H13">
         <v>-1</v>
@@ -1815,25 +1228,25 @@
         <v>131072</v>
       </c>
       <c r="T13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X13" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>262144</v>
       </c>
@@ -1841,19 +1254,19 @@
         <v>-1</v>
       </c>
       <c r="C14">
-        <v>48.005854999999997</v>
+        <v>48.005855</v>
       </c>
       <c r="D14">
         <v>-1</v>
       </c>
       <c r="E14">
-        <v>83.987384000000006</v>
+        <v>83.987384</v>
       </c>
       <c r="F14">
-        <v>2.3040999999999999E-2</v>
+        <v>0.023041</v>
       </c>
       <c r="G14">
-        <v>1.9866000000000002E-2</v>
+        <v>0.019866</v>
       </c>
       <c r="H14">
         <v>-1</v>
@@ -1892,127 +1305,127 @@
         <v>262144</v>
       </c>
       <c r="T14" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" t="s">
+        <v>16</v>
+      </c>
+      <c r="V14" t="s">
+        <v>16</v>
+      </c>
+      <c r="W14" t="s">
+        <v>16</v>
+      </c>
+      <c r="X14" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="U14" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" t="s">
-        <v>8</v>
-      </c>
-      <c r="X14" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="D17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>4</v>
-      </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M17" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S17" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X17" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1024</v>
       </c>
       <c r="B18">
-        <v>7.8799999999999996E-4</v>
+        <v>0.000788</v>
       </c>
       <c r="C18">
-        <v>7.1000000000000002E-4</v>
+        <v>0.00071</v>
       </c>
       <c r="D18">
-        <v>1.7E-5</v>
+        <v>0.000017</v>
       </c>
       <c r="E18">
-        <v>3.9999999999999998E-6</v>
+        <v>0.000004</v>
       </c>
       <c r="F18">
-        <v>3.3000000000000003E-5</v>
+        <v>0.000033</v>
       </c>
       <c r="G18">
-        <v>6.3999999999999997E-5</v>
+        <v>0.000064</v>
       </c>
       <c r="H18">
         <v>523776</v>
@@ -2051,45 +1464,45 @@
         <v>1024</v>
       </c>
       <c r="T18" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U18" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V18" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W18" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X18" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2048</v>
       </c>
       <c r="B19">
-        <v>3.019E-3</v>
+        <v>0.003019</v>
       </c>
       <c r="C19">
-        <v>2.7989999999999998E-3</v>
+        <v>0.002799</v>
       </c>
       <c r="D19">
-        <v>3.4E-5</v>
+        <v>0.000034</v>
       </c>
       <c r="E19">
-        <v>6.9999999999999999E-6</v>
+        <v>0.000007</v>
       </c>
       <c r="F19">
-        <v>6.7000000000000002E-5</v>
+        <v>0.000067</v>
       </c>
       <c r="G19">
-        <v>1.2400000000000001E-4</v>
+        <v>0.000124</v>
       </c>
       <c r="H19">
         <v>2096128</v>
@@ -2128,45 +1541,45 @@
         <v>2048</v>
       </c>
       <c r="T19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X19" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>4096</v>
       </c>
       <c r="B20">
-        <v>1.2126E-2</v>
+        <v>0.012126</v>
       </c>
       <c r="C20">
-        <v>1.1065999999999999E-2</v>
+        <v>0.011066</v>
       </c>
       <c r="D20">
-        <v>7.2999999999999999E-5</v>
+        <v>0.000073</v>
       </c>
       <c r="E20">
-        <v>1.2999999999999999E-5</v>
+        <v>0.000013</v>
       </c>
       <c r="F20">
-        <v>1.54E-4</v>
+        <v>0.000154</v>
       </c>
       <c r="G20">
-        <v>2.6699999999999998E-4</v>
+        <v>0.000267</v>
       </c>
       <c r="H20">
         <v>8386560</v>
@@ -2205,45 +1618,45 @@
         <v>4096</v>
       </c>
       <c r="T20" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U20" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V20" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W20" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X20" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y20" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>8192</v>
       </c>
       <c r="B21">
-        <v>4.7195000000000001E-2</v>
+        <v>0.047195</v>
       </c>
       <c r="C21">
-        <v>4.5185000000000003E-2</v>
+        <v>0.045185</v>
       </c>
       <c r="D21">
-        <v>1.7100000000000001E-4</v>
+        <v>0.000171</v>
       </c>
       <c r="E21">
-        <v>2.9E-5</v>
+        <v>0.000029</v>
       </c>
       <c r="F21">
-        <v>3.5799999999999997E-4</v>
+        <v>0.000358</v>
       </c>
       <c r="G21">
-        <v>5.4699999999999996E-4</v>
+        <v>0.000547</v>
       </c>
       <c r="H21">
         <v>33550336</v>
@@ -2282,25 +1695,25 @@
         <v>8192</v>
       </c>
       <c r="T21" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U21" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V21" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W21" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X21" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>16384</v>
       </c>
@@ -2308,19 +1721,19 @@
         <v>0.193297</v>
       </c>
       <c r="C22">
-        <v>0.17837800000000001</v>
+        <v>0.178378</v>
       </c>
       <c r="D22">
-        <v>3.3E-4</v>
+        <v>0.00033</v>
       </c>
       <c r="E22">
-        <v>5.3000000000000001E-5</v>
+        <v>0.000053</v>
       </c>
       <c r="F22">
-        <v>7.6999999999999996E-4</v>
+        <v>0.00077</v>
       </c>
       <c r="G22">
-        <v>1.1169999999999999E-3</v>
+        <v>0.001117</v>
       </c>
       <c r="H22">
         <v>134209536</v>
@@ -2359,25 +1772,25 @@
         <v>16384</v>
       </c>
       <c r="T22" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U22" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V22" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W22" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X22" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>32768</v>
       </c>
@@ -2385,19 +1798,19 @@
         <v>-1</v>
       </c>
       <c r="C23">
-        <v>0.71477199999999996</v>
+        <v>0.714772</v>
       </c>
       <c r="D23">
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>1.15E-4</v>
+        <v>0.000115</v>
       </c>
       <c r="F23">
-        <v>1.6659999999999999E-3</v>
+        <v>0.001666</v>
       </c>
       <c r="G23">
-        <v>2.1050000000000001E-3</v>
+        <v>0.002105</v>
       </c>
       <c r="H23">
         <v>-1</v>
@@ -2436,25 +1849,25 @@
         <v>32768</v>
       </c>
       <c r="T23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X23" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>65536</v>
       </c>
@@ -2468,13 +1881,13 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>2.2599999999999999E-4</v>
+        <v>0.000226</v>
       </c>
       <c r="F24">
-        <v>3.5990000000000002E-3</v>
+        <v>0.003599</v>
       </c>
       <c r="G24">
-        <v>4.3280000000000002E-3</v>
+        <v>0.004328</v>
       </c>
       <c r="H24">
         <v>-1</v>
@@ -2513,25 +1926,25 @@
         <v>65536</v>
       </c>
       <c r="T24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X24" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>131072</v>
       </c>
@@ -2545,13 +1958,13 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>4.6700000000000002E-4</v>
+        <v>0.000467</v>
       </c>
       <c r="F25">
-        <v>8.4910000000000003E-3</v>
+        <v>0.008491</v>
       </c>
       <c r="G25">
-        <v>8.9709999999999998E-3</v>
+        <v>0.008971</v>
       </c>
       <c r="H25">
         <v>-1</v>
@@ -2590,25 +2003,25 @@
         <v>131072</v>
       </c>
       <c r="T25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X25" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>262144</v>
       </c>
@@ -2616,19 +2029,19 @@
         <v>-1</v>
       </c>
       <c r="C26">
-        <v>45.650167000000003</v>
+        <v>45.650167</v>
       </c>
       <c r="D26">
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>9.0399999999999996E-4</v>
+        <v>0.000904</v>
       </c>
       <c r="F26">
-        <v>1.6069E-2</v>
+        <v>0.016069</v>
       </c>
       <c r="G26">
-        <v>1.9730999999999999E-2</v>
+        <v>0.019731</v>
       </c>
       <c r="H26">
         <v>-1</v>
@@ -2667,127 +2080,127 @@
         <v>262144</v>
       </c>
       <c r="T26" t="s">
+        <v>16</v>
+      </c>
+      <c r="U26" t="s">
+        <v>16</v>
+      </c>
+      <c r="V26" t="s">
+        <v>16</v>
+      </c>
+      <c r="W26" t="s">
+        <v>16</v>
+      </c>
+      <c r="X26" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
         <v>8</v>
       </c>
-      <c r="U26" t="s">
-        <v>8</v>
-      </c>
-      <c r="V26" t="s">
-        <v>8</v>
-      </c>
-      <c r="W26" t="s">
-        <v>8</v>
-      </c>
-      <c r="X26" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
       <c r="F29" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G29" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M29" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S29" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X29" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1024</v>
       </c>
       <c r="B30">
-        <v>1.983E-3</v>
+        <v>0.001983</v>
       </c>
       <c r="C30">
-        <v>7.2499999999999995E-4</v>
+        <v>0.000725</v>
       </c>
       <c r="D30">
-        <v>6.3999999999999997E-5</v>
+        <v>0.000064</v>
       </c>
       <c r="E30">
-        <v>5.8600000000000004E-4</v>
+        <v>0.000586</v>
       </c>
       <c r="F30">
-        <v>1.2799999999999999E-4</v>
+        <v>0.000128</v>
       </c>
       <c r="G30">
-        <v>4.3999999999999999E-5</v>
+        <v>0.000044</v>
       </c>
       <c r="H30">
         <v>523776</v>
@@ -2826,45 +2239,45 @@
         <v>1024</v>
       </c>
       <c r="T30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X30" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2048</v>
       </c>
       <c r="B31">
-        <v>7.1390000000000004E-3</v>
+        <v>0.007139</v>
       </c>
       <c r="C31">
-        <v>3.1909999999999998E-3</v>
+        <v>0.003191</v>
       </c>
       <c r="D31">
-        <v>1.2799999999999999E-4</v>
+        <v>0.000128</v>
       </c>
       <c r="E31">
-        <v>2.4399999999999999E-3</v>
+        <v>0.00244</v>
       </c>
       <c r="F31">
-        <v>2.3000000000000001E-4</v>
+        <v>0.00023</v>
       </c>
       <c r="G31">
-        <v>7.1000000000000005E-5</v>
+        <v>0.000071</v>
       </c>
       <c r="H31">
         <v>2096128</v>
@@ -2903,45 +2316,45 @@
         <v>2048</v>
       </c>
       <c r="T31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X31" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>4096</v>
       </c>
       <c r="B32">
-        <v>2.9315999999999998E-2</v>
+        <v>0.029316</v>
       </c>
       <c r="C32">
-        <v>1.1318999999999999E-2</v>
+        <v>0.011319</v>
       </c>
       <c r="D32">
-        <v>2.61E-4</v>
+        <v>0.000261</v>
       </c>
       <c r="E32">
-        <v>1.0172E-2</v>
+        <v>0.010172</v>
       </c>
       <c r="F32">
-        <v>5.1999999999999995E-4</v>
+        <v>0.00052</v>
       </c>
       <c r="G32">
-        <v>7.0799999999999997E-4</v>
+        <v>0.000708</v>
       </c>
       <c r="H32">
         <v>8386560</v>
@@ -2980,45 +2393,45 @@
         <v>4096</v>
       </c>
       <c r="T32" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U32" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V32" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W32" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X32" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>8192</v>
       </c>
       <c r="B33">
-        <v>0.12571099999999999</v>
+        <v>0.125711</v>
       </c>
       <c r="C33">
-        <v>4.5740999999999997E-2</v>
+        <v>0.045741</v>
       </c>
       <c r="D33">
-        <v>5.0600000000000005E-4</v>
+        <v>0.000506</v>
       </c>
       <c r="E33">
-        <v>4.0379999999999999E-2</v>
+        <v>0.04038</v>
       </c>
       <c r="F33">
-        <v>1.2620000000000001E-3</v>
+        <v>0.001262</v>
       </c>
       <c r="G33">
-        <v>2.8299999999999999E-4</v>
+        <v>0.000283</v>
       </c>
       <c r="H33">
         <v>33550336</v>
@@ -3057,45 +2470,45 @@
         <v>8192</v>
       </c>
       <c r="T33" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U33" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V33" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W33" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X33" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>16384</v>
       </c>
       <c r="B34">
-        <v>0.58507299999999995</v>
+        <v>0.585073</v>
       </c>
       <c r="C34">
-        <v>0.18082300000000001</v>
+        <v>0.180823</v>
       </c>
       <c r="D34">
-        <v>1.0250000000000001E-3</v>
+        <v>0.001025</v>
       </c>
       <c r="E34">
-        <v>0.15845899999999999</v>
+        <v>0.158459</v>
       </c>
       <c r="F34">
-        <v>2.7910000000000001E-3</v>
+        <v>0.002791</v>
       </c>
       <c r="G34">
-        <v>6.1600000000000001E-4</v>
+        <v>0.000616</v>
       </c>
       <c r="H34">
         <v>134209536</v>
@@ -3134,25 +2547,25 @@
         <v>16384</v>
       </c>
       <c r="T34" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U34" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V34" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W34" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X34" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>32768</v>
       </c>
@@ -3160,19 +2573,19 @@
         <v>-1</v>
       </c>
       <c r="C35">
-        <v>0.71642700000000004</v>
+        <v>0.716427</v>
       </c>
       <c r="D35">
         <v>-1</v>
       </c>
       <c r="E35">
-        <v>0.64096900000000001</v>
+        <v>0.640969</v>
       </c>
       <c r="F35">
-        <v>6.8669999999999998E-3</v>
+        <v>0.006867</v>
       </c>
       <c r="G35">
-        <v>1.2459999999999999E-3</v>
+        <v>0.001246</v>
       </c>
       <c r="H35">
         <v>-1</v>
@@ -3211,25 +2624,25 @@
         <v>32768</v>
       </c>
       <c r="T35" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U35" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V35" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W35" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X35" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>65536</v>
       </c>
@@ -3237,19 +2650,19 @@
         <v>-1</v>
       </c>
       <c r="C36">
-        <v>2.9412229999999999</v>
+        <v>2.941223</v>
       </c>
       <c r="D36">
         <v>-1</v>
       </c>
       <c r="E36">
-        <v>2.5589520000000001</v>
+        <v>2.558952</v>
       </c>
       <c r="F36">
-        <v>1.3627999999999999E-2</v>
+        <v>0.013628</v>
       </c>
       <c r="G36">
-        <v>2.366E-3</v>
+        <v>0.002366</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3288,25 +2701,25 @@
         <v>65536</v>
       </c>
       <c r="T36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X36" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>131072</v>
       </c>
@@ -3323,10 +2736,10 @@
         <v>10.220518</v>
       </c>
       <c r="F37">
-        <v>2.8645E-2</v>
+        <v>0.028645</v>
       </c>
       <c r="G37">
-        <v>4.816E-3</v>
+        <v>0.004816</v>
       </c>
       <c r="H37">
         <v>-1</v>
@@ -3365,25 +2778,25 @@
         <v>131072</v>
       </c>
       <c r="T37" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U37" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V37" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W37" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X37" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>262144</v>
       </c>
@@ -3391,7 +2804,7 @@
         <v>-1</v>
       </c>
       <c r="C38">
-        <v>45.866700000000002</v>
+        <v>45.8667</v>
       </c>
       <c r="D38">
         <v>-1</v>
@@ -3400,10 +2813,10 @@
         <v>40.839343</v>
       </c>
       <c r="F38">
-        <v>5.4441000000000003E-2</v>
+        <v>0.054441</v>
       </c>
       <c r="G38">
-        <v>9.6069999999999992E-3</v>
+        <v>0.009607</v>
       </c>
       <c r="H38">
         <v>-1</v>
@@ -3442,127 +2855,127 @@
         <v>262144</v>
       </c>
       <c r="T38" t="s">
+        <v>16</v>
+      </c>
+      <c r="U38" t="s">
+        <v>16</v>
+      </c>
+      <c r="V38" t="s">
+        <v>16</v>
+      </c>
+      <c r="W38" t="s">
+        <v>16</v>
+      </c>
+      <c r="X38" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
         <v>8</v>
       </c>
-      <c r="U38" t="s">
-        <v>8</v>
-      </c>
-      <c r="V38" t="s">
-        <v>8</v>
-      </c>
-      <c r="W38" t="s">
-        <v>8</v>
-      </c>
-      <c r="X38" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+      <c r="D41" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>29</v>
-      </c>
-      <c r="B41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" t="s">
-        <v>6</v>
-      </c>
       <c r="G41" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M41" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S41" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T41" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U41" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V41" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W41" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X41" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1024</v>
       </c>
       <c r="B42">
-        <v>1.884E-3</v>
+        <v>0.001884</v>
       </c>
       <c r="C42">
-        <v>7.2499999999999995E-4</v>
+        <v>0.000725</v>
       </c>
       <c r="D42">
-        <v>6.3E-5</v>
+        <v>0.000063</v>
       </c>
       <c r="E42">
-        <v>6.4000000000000005E-4</v>
+        <v>0.00064</v>
       </c>
       <c r="F42">
-        <v>9.8999999999999994E-5</v>
+        <v>0.000099</v>
       </c>
       <c r="G42">
-        <v>4.6E-5</v>
+        <v>0.000046</v>
       </c>
       <c r="H42">
         <v>523776</v>
@@ -3601,45 +3014,45 @@
         <v>1024</v>
       </c>
       <c r="T42" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U42" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V42" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W42" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X42" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2048</v>
       </c>
       <c r="B43">
-        <v>7.0369999999999999E-3</v>
+        <v>0.007037</v>
       </c>
       <c r="C43">
-        <v>2.859E-3</v>
+        <v>0.002859</v>
       </c>
       <c r="D43">
-        <v>1.93E-4</v>
+        <v>0.000193</v>
       </c>
       <c r="E43">
-        <v>2.467E-3</v>
+        <v>0.002467</v>
       </c>
       <c r="F43">
-        <v>2.3499999999999999E-4</v>
+        <v>0.000235</v>
       </c>
       <c r="G43">
-        <v>8.2999999999999998E-5</v>
+        <v>0.000083</v>
       </c>
       <c r="H43">
         <v>2096128</v>
@@ -3678,45 +3091,45 @@
         <v>2048</v>
       </c>
       <c r="T43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X43" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>4096</v>
       </c>
       <c r="B44">
-        <v>2.8660000000000001E-2</v>
+        <v>0.02866</v>
       </c>
       <c r="C44">
-        <v>1.1407E-2</v>
+        <v>0.011407</v>
       </c>
       <c r="D44">
-        <v>2.3000000000000001E-4</v>
+        <v>0.00023</v>
       </c>
       <c r="E44">
-        <v>1.0019999999999999E-2</v>
+        <v>0.01002</v>
       </c>
       <c r="F44">
-        <v>5.0699999999999996E-4</v>
+        <v>0.000507</v>
       </c>
       <c r="G44">
-        <v>1.2799999999999999E-4</v>
+        <v>0.000128</v>
       </c>
       <c r="H44">
         <v>8386560</v>
@@ -3755,45 +3168,45 @@
         <v>4096</v>
       </c>
       <c r="T44" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U44" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V44" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W44" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X44" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>8192</v>
       </c>
       <c r="B45">
-        <v>0.12545799999999999</v>
+        <v>0.125458</v>
       </c>
       <c r="C45">
-        <v>4.5109999999999997E-2</v>
+        <v>0.04511</v>
       </c>
       <c r="D45">
-        <v>5.4799999999999998E-4</v>
+        <v>0.000548</v>
       </c>
       <c r="E45">
-        <v>4.0016000000000003E-2</v>
+        <v>0.040016</v>
       </c>
       <c r="F45">
-        <v>1.1360000000000001E-3</v>
+        <v>0.001136</v>
       </c>
       <c r="G45">
-        <v>2.5999999999999998E-4</v>
+        <v>0.00026</v>
       </c>
       <c r="H45">
         <v>33550336</v>
@@ -3832,45 +3245,45 @@
         <v>8192</v>
       </c>
       <c r="T45" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U45" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V45" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W45" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X45" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>16384</v>
       </c>
       <c r="B46">
-        <v>0.59117699999999995</v>
+        <v>0.591177</v>
       </c>
       <c r="C46">
-        <v>0.17780299999999999</v>
+        <v>0.177803</v>
       </c>
       <c r="D46">
-        <v>9.8200000000000002E-4</v>
+        <v>0.000982</v>
       </c>
       <c r="E46">
         <v>0.153394</v>
       </c>
       <c r="F46">
-        <v>2.2209999999999999E-3</v>
+        <v>0.002221</v>
       </c>
       <c r="G46">
-        <v>4.9899999999999999E-4</v>
+        <v>0.000499</v>
       </c>
       <c r="H46">
         <v>134209536</v>
@@ -3909,25 +3322,25 @@
         <v>16384</v>
       </c>
       <c r="T46" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U46" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V46" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W46" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X46" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>32768</v>
       </c>
@@ -3935,19 +3348,19 @@
         <v>-1</v>
       </c>
       <c r="C47">
-        <v>0.71110300000000004</v>
+        <v>0.711103</v>
       </c>
       <c r="D47">
         <v>-1</v>
       </c>
       <c r="E47">
-        <v>0.62819899999999995</v>
+        <v>0.628199</v>
       </c>
       <c r="F47">
-        <v>4.8500000000000001E-3</v>
+        <v>0.00485</v>
       </c>
       <c r="G47">
-        <v>9.2800000000000001E-4</v>
+        <v>0.000928</v>
       </c>
       <c r="H47">
         <v>-1</v>
@@ -3986,25 +3399,25 @@
         <v>32768</v>
       </c>
       <c r="T47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X47" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y47" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>65536</v>
       </c>
@@ -4018,13 +3431,13 @@
         <v>-1</v>
       </c>
       <c r="E48">
-        <v>2.5222880000000001</v>
+        <v>2.522288</v>
       </c>
       <c r="F48">
-        <v>9.9279999999999993E-3</v>
+        <v>0.009928</v>
       </c>
       <c r="G48">
-        <v>2.2269999999999998E-3</v>
+        <v>0.002227</v>
       </c>
       <c r="H48">
         <v>-1</v>
@@ -4063,25 +3476,25 @@
         <v>65536</v>
       </c>
       <c r="T48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X48" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y48" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>131072</v>
       </c>
@@ -4089,19 +3502,19 @@
         <v>-1</v>
       </c>
       <c r="C49">
-        <v>11.463006999999999</v>
+        <v>11.463007</v>
       </c>
       <c r="D49">
         <v>-1</v>
       </c>
       <c r="E49">
-        <v>10.034739999999999</v>
+        <v>10.03474</v>
       </c>
       <c r="F49">
-        <v>2.2089000000000001E-2</v>
+        <v>0.022089</v>
       </c>
       <c r="G49">
-        <v>3.702E-3</v>
+        <v>0.003702</v>
       </c>
       <c r="H49">
         <v>-1</v>
@@ -4140,25 +3553,25 @@
         <v>131072</v>
       </c>
       <c r="T49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X49" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y49" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>262144</v>
       </c>
@@ -4166,19 +3579,19 @@
         <v>-1</v>
       </c>
       <c r="C50">
-        <v>45.806615000000001</v>
+        <v>45.806615</v>
       </c>
       <c r="D50">
         <v>-1</v>
       </c>
       <c r="E50">
-        <v>39.934750999999999</v>
+        <v>39.934751</v>
       </c>
       <c r="F50">
-        <v>4.6649999999999997E-2</v>
+        <v>0.04665</v>
       </c>
       <c r="G50">
-        <v>7.4520000000000003E-3</v>
+        <v>0.007452</v>
       </c>
       <c r="H50">
         <v>-1</v>
@@ -4217,127 +3630,127 @@
         <v>262144</v>
       </c>
       <c r="T50" t="s">
+        <v>16</v>
+      </c>
+      <c r="U50" t="s">
+        <v>16</v>
+      </c>
+      <c r="V50" t="s">
+        <v>16</v>
+      </c>
+      <c r="W50" t="s">
+        <v>16</v>
+      </c>
+      <c r="X50" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
         <v>8</v>
       </c>
-      <c r="U50" t="s">
-        <v>8</v>
-      </c>
-      <c r="V50" t="s">
-        <v>8</v>
-      </c>
-      <c r="W50" t="s">
-        <v>8</v>
-      </c>
-      <c r="X50" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="D53" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" t="s">
-        <v>4</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" t="s">
-        <v>7</v>
-      </c>
       <c r="H53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M53" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S53" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X53" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y53" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>1024</v>
       </c>
       <c r="B54">
-        <v>2.3760000000000001E-3</v>
+        <v>0.002376</v>
       </c>
       <c r="C54">
-        <v>7.3099999999999999E-4</v>
+        <v>0.000731</v>
       </c>
       <c r="D54">
-        <v>1.9000000000000001E-5</v>
+        <v>0.000019</v>
       </c>
       <c r="E54">
-        <v>1.2689999999999999E-3</v>
+        <v>0.001269</v>
       </c>
       <c r="F54">
-        <v>5.3999999999999998E-5</v>
+        <v>0.000054</v>
       </c>
       <c r="G54">
-        <v>6.3999999999999997E-5</v>
+        <v>0.000064</v>
       </c>
       <c r="H54">
         <v>523776</v>
@@ -4376,45 +3789,45 @@
         <v>1024</v>
       </c>
       <c r="T54" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U54" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V54" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W54" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X54" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2048</v>
       </c>
       <c r="B55">
-        <v>9.6889999999999997E-3</v>
+        <v>0.009689</v>
       </c>
       <c r="C55">
-        <v>3.0599999999999998E-3</v>
+        <v>0.00306</v>
       </c>
       <c r="D55">
-        <v>3.8999999999999999E-5</v>
+        <v>0.000039</v>
       </c>
       <c r="E55">
-        <v>5.0819999999999997E-3</v>
+        <v>0.005082</v>
       </c>
       <c r="F55">
-        <v>1.55E-4</v>
+        <v>0.000155</v>
       </c>
       <c r="G55">
-        <v>1.3799999999999999E-4</v>
+        <v>0.000138</v>
       </c>
       <c r="H55">
         <v>2096128</v>
@@ -4453,45 +3866,45 @@
         <v>2048</v>
       </c>
       <c r="T55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X55" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y55" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>4096</v>
       </c>
       <c r="B56">
-        <v>4.0611000000000001E-2</v>
+        <v>0.040611</v>
       </c>
       <c r="C56">
-        <v>1.1804E-2</v>
+        <v>0.011804</v>
       </c>
       <c r="D56">
-        <v>8.7000000000000001E-5</v>
+        <v>0.000087</v>
       </c>
       <c r="E56">
-        <v>2.1597000000000002E-2</v>
+        <v>0.021597</v>
       </c>
       <c r="F56">
-        <v>2.4600000000000002E-4</v>
+        <v>0.000246</v>
       </c>
       <c r="G56">
-        <v>2.9E-4</v>
+        <v>0.00029</v>
       </c>
       <c r="H56">
         <v>8386560</v>
@@ -4530,45 +3943,45 @@
         <v>4096</v>
       </c>
       <c r="T56" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U56" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V56" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W56" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X56" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y56" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>8192</v>
       </c>
       <c r="B57">
-        <v>0.16320000000000001</v>
+        <v>0.1632</v>
       </c>
       <c r="C57">
-        <v>4.8874000000000001E-2</v>
+        <v>0.048874</v>
       </c>
       <c r="D57">
-        <v>1.7799999999999999E-4</v>
+        <v>0.000178</v>
       </c>
       <c r="E57">
-        <v>8.2447000000000006E-2</v>
+        <v>0.082447</v>
       </c>
       <c r="F57">
-        <v>7.1699999999999997E-4</v>
+        <v>0.000717</v>
       </c>
       <c r="G57">
-        <v>5.9599999999999996E-4</v>
+        <v>0.000596</v>
       </c>
       <c r="H57">
         <v>33550336</v>
@@ -4607,45 +4020,45 @@
         <v>8192</v>
       </c>
       <c r="T57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X57" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y57" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>16384</v>
       </c>
       <c r="B58">
-        <v>0.64638700000000004</v>
+        <v>0.646387</v>
       </c>
       <c r="C58">
-        <v>0.19312000000000001</v>
+        <v>0.19312</v>
       </c>
       <c r="D58">
-        <v>3.7500000000000001E-4</v>
+        <v>0.000375</v>
       </c>
       <c r="E58">
-        <v>0.32929700000000001</v>
+        <v>0.329297</v>
       </c>
       <c r="F58">
-        <v>1.1329999999999999E-3</v>
+        <v>0.001133</v>
       </c>
       <c r="G58">
-        <v>1.1119999999999999E-3</v>
+        <v>0.001112</v>
       </c>
       <c r="H58">
         <v>134209536</v>
@@ -4684,25 +4097,25 @@
         <v>16384</v>
       </c>
       <c r="T58" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U58" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V58" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W58" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X58" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y58" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>32768</v>
       </c>
@@ -4710,19 +4123,19 @@
         <v>-1</v>
       </c>
       <c r="C59">
-        <v>0.77322199999999996</v>
+        <v>0.773222</v>
       </c>
       <c r="D59">
         <v>-1</v>
       </c>
       <c r="E59">
-        <v>1.3105880000000001</v>
+        <v>1.310588</v>
       </c>
       <c r="F59">
-        <v>2.8379999999999998E-3</v>
+        <v>0.002838</v>
       </c>
       <c r="G59">
-        <v>2.1419999999999998E-3</v>
+        <v>0.002142</v>
       </c>
       <c r="H59">
         <v>-1</v>
@@ -4761,25 +4174,25 @@
         <v>32768</v>
       </c>
       <c r="T59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X59" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y59" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>65536</v>
       </c>
@@ -4787,19 +4200,19 @@
         <v>-1</v>
       </c>
       <c r="C60">
-        <v>3.0799859999999999</v>
+        <v>3.079986</v>
       </c>
       <c r="D60">
         <v>-1</v>
       </c>
       <c r="E60">
-        <v>5.2482499999999996</v>
+        <v>5.24825</v>
       </c>
       <c r="F60">
-        <v>5.6899999999999997E-3</v>
+        <v>0.00569</v>
       </c>
       <c r="G60">
-        <v>4.4209999999999996E-3</v>
+        <v>0.004421</v>
       </c>
       <c r="H60">
         <v>-1</v>
@@ -4838,25 +4251,25 @@
         <v>65536</v>
       </c>
       <c r="T60" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U60" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V60" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W60" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X60" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y60" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>131072</v>
       </c>
@@ -4870,13 +4283,13 @@
         <v>-1</v>
       </c>
       <c r="E61">
-        <v>21.080480000000001</v>
+        <v>21.08048</v>
       </c>
       <c r="F61">
-        <v>1.1565000000000001E-2</v>
+        <v>0.011565</v>
       </c>
       <c r="G61">
-        <v>9.1450000000000004E-3</v>
+        <v>0.009145</v>
       </c>
       <c r="H61">
         <v>-1</v>
@@ -4915,25 +4328,25 @@
         <v>131072</v>
       </c>
       <c r="T61" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U61" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V61" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W61" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X61" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y61" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>262144</v>
       </c>
@@ -4941,19 +4354,19 @@
         <v>-1</v>
       </c>
       <c r="C62">
-        <v>49.339424999999999</v>
+        <v>49.339425</v>
       </c>
       <c r="D62">
         <v>-1</v>
       </c>
       <c r="E62">
-        <v>84.382172999999995</v>
+        <v>84.382173</v>
       </c>
       <c r="F62">
-        <v>2.5489000000000001E-2</v>
+        <v>0.025489</v>
       </c>
       <c r="G62">
-        <v>2.0500999999999998E-2</v>
+        <v>0.020501</v>
       </c>
       <c r="H62">
         <v>-1</v>
@@ -4992,127 +4405,127 @@
         <v>262144</v>
       </c>
       <c r="T62" t="s">
+        <v>16</v>
+      </c>
+      <c r="U62" t="s">
+        <v>16</v>
+      </c>
+      <c r="V62" t="s">
+        <v>16</v>
+      </c>
+      <c r="W62" t="s">
+        <v>16</v>
+      </c>
+      <c r="X62" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" t="s">
         <v>8</v>
       </c>
-      <c r="U62" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" t="s">
-        <v>8</v>
-      </c>
-      <c r="W62" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y62" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>12</v>
+      </c>
+      <c r="H65" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" t="s">
-        <v>2</v>
-      </c>
-      <c r="C65" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" t="s">
-        <v>4</v>
-      </c>
-      <c r="E65" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" t="s">
-        <v>7</v>
-      </c>
-      <c r="H65" t="s">
-        <v>31</v>
-      </c>
       <c r="I65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="J65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="L65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="M65" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S65" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X65" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1024</v>
       </c>
       <c r="B66">
-        <v>7.9299999999999998E-4</v>
+        <v>0.000793</v>
       </c>
       <c r="C66">
-        <v>7.7300000000000003E-4</v>
+        <v>0.000773</v>
       </c>
       <c r="D66">
-        <v>1.9000000000000001E-5</v>
+        <v>0.000019</v>
       </c>
       <c r="E66">
-        <v>3.0000000000000001E-6</v>
+        <v>0.000003</v>
       </c>
       <c r="F66">
-        <v>3.4E-5</v>
+        <v>0.000034</v>
       </c>
       <c r="G66">
-        <v>6.6000000000000005E-5</v>
+        <v>0.000066</v>
       </c>
       <c r="H66">
         <v>523776</v>
@@ -5151,45 +4564,45 @@
         <v>1024</v>
       </c>
       <c r="T66" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U66" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V66" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W66" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X66" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y66" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2048</v>
       </c>
       <c r="B67">
-        <v>3.2550000000000001E-3</v>
+        <v>0.003255</v>
       </c>
       <c r="C67">
-        <v>2.862E-3</v>
+        <v>0.002862</v>
       </c>
       <c r="D67">
-        <v>3.8999999999999999E-5</v>
+        <v>0.000039</v>
       </c>
       <c r="E67">
-        <v>7.9999999999999996E-6</v>
+        <v>0.000008</v>
       </c>
       <c r="F67">
-        <v>7.7999999999999999E-5</v>
+        <v>0.000078</v>
       </c>
       <c r="G67">
-        <v>1.44E-4</v>
+        <v>0.000144</v>
       </c>
       <c r="H67">
         <v>2096128</v>
@@ -5228,45 +4641,45 @@
         <v>2048</v>
       </c>
       <c r="T67" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U67" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V67" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W67" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X67" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y67" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>4096</v>
       </c>
       <c r="B68">
-        <v>1.2076E-2</v>
+        <v>0.012076</v>
       </c>
       <c r="C68">
-        <v>1.1480000000000001E-2</v>
+        <v>0.01148</v>
       </c>
       <c r="D68">
-        <v>7.1000000000000005E-5</v>
+        <v>0.000071</v>
       </c>
       <c r="E68">
-        <v>1.5E-5</v>
+        <v>0.000015</v>
       </c>
       <c r="F68">
-        <v>1.6799999999999999E-4</v>
+        <v>0.000168</v>
       </c>
       <c r="G68">
-        <v>2.6600000000000001E-4</v>
+        <v>0.000266</v>
       </c>
       <c r="H68">
         <v>8386560</v>
@@ -5305,45 +4718,45 @@
         <v>4096</v>
       </c>
       <c r="T68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X68" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y68" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>8192</v>
       </c>
       <c r="B69">
-        <v>4.9925999999999998E-2</v>
+        <v>0.049926</v>
       </c>
       <c r="C69">
-        <v>4.6025999999999997E-2</v>
+        <v>0.046026</v>
       </c>
       <c r="D69">
-        <v>1.66E-4</v>
+        <v>0.000166</v>
       </c>
       <c r="E69">
-        <v>2.8E-5</v>
+        <v>0.000028</v>
       </c>
       <c r="F69">
-        <v>4.5100000000000001E-4</v>
+        <v>0.000451</v>
       </c>
       <c r="G69">
-        <v>5.22E-4</v>
+        <v>0.000522</v>
       </c>
       <c r="H69">
         <v>33550336</v>
@@ -5382,25 +4795,25 @@
         <v>8192</v>
       </c>
       <c r="T69" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U69" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V69" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W69" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X69" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y69" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>16384</v>
       </c>
@@ -5411,16 +4824,16 @@
         <v>0.186974</v>
       </c>
       <c r="D70">
-        <v>3.57E-4</v>
+        <v>0.000357</v>
       </c>
       <c r="E70">
-        <v>5.5000000000000002E-5</v>
+        <v>0.000055</v>
       </c>
       <c r="F70">
-        <v>7.9299999999999998E-4</v>
+        <v>0.000793</v>
       </c>
       <c r="G70">
-        <v>1.193E-3</v>
+        <v>0.001193</v>
       </c>
       <c r="H70">
         <v>134209536</v>
@@ -5459,25 +4872,25 @@
         <v>16384</v>
       </c>
       <c r="T70" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U70" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V70" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W70" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X70" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y70" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>32768</v>
       </c>
@@ -5485,19 +4898,19 @@
         <v>-1</v>
       </c>
       <c r="C71">
-        <v>0.74215500000000001</v>
+        <v>0.742155</v>
       </c>
       <c r="D71">
         <v>-1</v>
       </c>
       <c r="E71">
-        <v>1.1E-4</v>
+        <v>0.00011</v>
       </c>
       <c r="F71">
-        <v>1.7849999999999999E-3</v>
+        <v>0.001785</v>
       </c>
       <c r="G71">
-        <v>2.2309999999999999E-3</v>
+        <v>0.002231</v>
       </c>
       <c r="H71">
         <v>-1</v>
@@ -5536,25 +4949,25 @@
         <v>32768</v>
       </c>
       <c r="T71" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U71" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V71" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W71" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X71" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y71" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>65536</v>
       </c>
@@ -5568,13 +4981,13 @@
         <v>-1</v>
       </c>
       <c r="E72">
-        <v>2.1800000000000001E-4</v>
+        <v>0.000218</v>
       </c>
       <c r="F72">
-        <v>3.614E-3</v>
+        <v>0.003614</v>
       </c>
       <c r="G72">
-        <v>4.3369999999999997E-3</v>
+        <v>0.004337</v>
       </c>
       <c r="H72">
         <v>-1</v>
@@ -5613,25 +5026,25 @@
         <v>65536</v>
       </c>
       <c r="T72" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U72" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V72" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W72" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X72" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y72" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>131072</v>
       </c>
@@ -5645,13 +5058,13 @@
         <v>-1</v>
       </c>
       <c r="E73">
-        <v>4.84E-4</v>
+        <v>0.000484</v>
       </c>
       <c r="F73">
-        <v>8.0700000000000008E-3</v>
+        <v>0.00807</v>
       </c>
       <c r="G73">
-        <v>8.5760000000000003E-3</v>
+        <v>0.008576</v>
       </c>
       <c r="H73">
         <v>-1</v>
@@ -5690,25 +5103,25 @@
         <v>131072</v>
       </c>
       <c r="T73" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U73" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V73" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W73" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X73" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y73" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>262144</v>
       </c>
@@ -5722,13 +5135,13 @@
         <v>-1</v>
       </c>
       <c r="E74">
-        <v>9.7599999999999998E-4</v>
+        <v>0.000976</v>
       </c>
       <c r="F74">
-        <v>1.7596000000000001E-2</v>
+        <v>0.017596</v>
       </c>
       <c r="G74">
-        <v>1.7610000000000001E-2</v>
+        <v>0.01761</v>
       </c>
       <c r="H74">
         <v>-1</v>
@@ -5767,127 +5180,127 @@
         <v>262144</v>
       </c>
       <c r="T74" t="s">
+        <v>16</v>
+      </c>
+      <c r="U74" t="s">
+        <v>16</v>
+      </c>
+      <c r="V74" t="s">
+        <v>16</v>
+      </c>
+      <c r="W74" t="s">
+        <v>16</v>
+      </c>
+      <c r="X74" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
         <v>8</v>
       </c>
-      <c r="U74" t="s">
-        <v>8</v>
-      </c>
-      <c r="V74" t="s">
-        <v>8</v>
-      </c>
-      <c r="W74" t="s">
-        <v>8</v>
-      </c>
-      <c r="X74" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y74" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="D77" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H77" t="s">
+        <v>13</v>
+      </c>
+      <c r="I77" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" t="s">
+        <v>13</v>
+      </c>
+      <c r="L77" t="s">
+        <v>13</v>
+      </c>
+      <c r="M77" t="s">
+        <v>13</v>
+      </c>
+      <c r="N77" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>29</v>
-      </c>
-      <c r="B77" t="s">
-        <v>2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" t="s">
-        <v>4</v>
-      </c>
-      <c r="E77" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" t="s">
-        <v>7</v>
-      </c>
-      <c r="H77" t="s">
-        <v>31</v>
-      </c>
-      <c r="I77" t="s">
-        <v>31</v>
-      </c>
-      <c r="J77" t="s">
-        <v>31</v>
-      </c>
-      <c r="K77" t="s">
-        <v>31</v>
-      </c>
-      <c r="L77" t="s">
-        <v>31</v>
-      </c>
-      <c r="M77" t="s">
-        <v>31</v>
-      </c>
-      <c r="N77" t="s">
-        <v>32</v>
-      </c>
       <c r="O77" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P77" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="Q77" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="R77" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="S77" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="T77" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="U77" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V77" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W77" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X77" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y77" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1024</v>
       </c>
       <c r="B78">
-        <v>1.895E-3</v>
+        <v>0.001895</v>
       </c>
       <c r="C78">
-        <v>7.7999999999999999E-4</v>
+        <v>0.00078</v>
       </c>
       <c r="D78">
-        <v>9.7E-5</v>
+        <v>0.000097</v>
       </c>
       <c r="E78">
-        <v>7.5799999999999999E-4</v>
+        <v>0.000758</v>
       </c>
       <c r="F78">
-        <v>1.47E-4</v>
+        <v>0.000147</v>
       </c>
       <c r="G78">
-        <v>9.41E-4</v>
+        <v>0.000941</v>
       </c>
       <c r="H78">
         <v>523776</v>
@@ -5926,45 +5339,45 @@
         <v>1792</v>
       </c>
       <c r="T78" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U78" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V78" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W78" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X78" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y78" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2048</v>
       </c>
       <c r="B79">
-        <v>7.6270000000000001E-3</v>
+        <v>0.007627</v>
       </c>
       <c r="C79">
-        <v>3.0209999999999998E-3</v>
+        <v>0.003021</v>
       </c>
       <c r="D79">
-        <v>1.92E-4</v>
+        <v>0.000192</v>
       </c>
       <c r="E79">
-        <v>2.66E-3</v>
+        <v>0.00266</v>
       </c>
       <c r="F79">
-        <v>3.9199999999999999E-4</v>
+        <v>0.000392</v>
       </c>
       <c r="G79">
-        <v>1.6899999999999999E-4</v>
+        <v>0.000169</v>
       </c>
       <c r="H79">
         <v>2096128</v>
@@ -6003,45 +5416,45 @@
         <v>3644</v>
       </c>
       <c r="T79" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U79" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V79" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W79" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X79" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y79" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>4096</v>
       </c>
       <c r="B80">
-        <v>3.1199999999999999E-2</v>
+        <v>0.0312</v>
       </c>
       <c r="C80">
-        <v>1.1976000000000001E-2</v>
+        <v>0.011976</v>
       </c>
       <c r="D80">
-        <v>4.0900000000000002E-4</v>
+        <v>0.000409</v>
       </c>
       <c r="E80">
-        <v>1.0553999999999999E-2</v>
+        <v>0.010554</v>
       </c>
       <c r="F80">
-        <v>9.6000000000000002E-4</v>
+        <v>0.00096</v>
       </c>
       <c r="G80">
-        <v>3.9199999999999999E-4</v>
+        <v>0.000392</v>
       </c>
       <c r="H80">
         <v>8386560</v>
@@ -6080,45 +5493,45 @@
         <v>7027</v>
       </c>
       <c r="T80" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U80" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V80" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W80" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X80" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y80" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>8192</v>
       </c>
       <c r="B81">
-        <v>0.14058200000000001</v>
+        <v>0.140582</v>
       </c>
       <c r="C81">
-        <v>4.7531999999999998E-2</v>
+        <v>0.047532</v>
       </c>
       <c r="D81">
-        <v>8.43E-4</v>
+        <v>0.000843</v>
       </c>
       <c r="E81">
-        <v>4.1206E-2</v>
+        <v>0.041206</v>
       </c>
       <c r="F81">
-        <v>2.3800000000000002E-3</v>
+        <v>0.00238</v>
       </c>
       <c r="G81">
-        <v>8.0099999999999995E-4</v>
+        <v>0.000801</v>
       </c>
       <c r="H81">
         <v>33550336</v>
@@ -6157,45 +5570,45 @@
         <v>14489</v>
       </c>
       <c r="T81" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U81" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V81" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W81" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X81" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y81" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>16384</v>
       </c>
       <c r="B82">
-        <v>0.68259899999999996</v>
+        <v>0.682599</v>
       </c>
       <c r="C82">
-        <v>0.18573500000000001</v>
+        <v>0.185735</v>
       </c>
       <c r="D82">
-        <v>2.0079999999999998E-3</v>
+        <v>0.002008</v>
       </c>
       <c r="E82">
         <v>0.165461</v>
       </c>
       <c r="F82">
-        <v>5.8079999999999998E-3</v>
+        <v>0.005808</v>
       </c>
       <c r="G82">
-        <v>1.521E-3</v>
+        <v>0.001521</v>
       </c>
       <c r="H82">
         <v>134209536</v>
@@ -6234,25 +5647,25 @@
         <v>28726</v>
       </c>
       <c r="T82" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U82" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V82" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W82" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X82" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y82" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>32768</v>
       </c>
@@ -6269,10 +5682,10 @@
         <v>0.666601</v>
       </c>
       <c r="F83">
-        <v>1.4229E-2</v>
+        <v>0.014229</v>
       </c>
       <c r="G83">
-        <v>3.2200000000000002E-3</v>
+        <v>0.00322</v>
       </c>
       <c r="H83">
         <v>-1</v>
@@ -6311,25 +5724,25 @@
         <v>57023</v>
       </c>
       <c r="T83" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U83" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V83" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W83" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X83" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y83" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>65536</v>
       </c>
@@ -6343,13 +5756,13 @@
         <v>-1</v>
       </c>
       <c r="E84">
-        <v>2.6448160000000001</v>
+        <v>2.644816</v>
       </c>
       <c r="F84">
-        <v>3.5004E-2</v>
+        <v>0.035004</v>
       </c>
       <c r="G84">
-        <v>7.1720000000000004E-3</v>
+        <v>0.007172</v>
       </c>
       <c r="H84">
         <v>-1</v>
@@ -6388,25 +5801,25 @@
         <v>114229</v>
       </c>
       <c r="T84" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U84" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V84" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W84" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X84" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y84" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>131072</v>
       </c>
@@ -6420,13 +5833,13 @@
         <v>-1</v>
       </c>
       <c r="E85">
-        <v>10.513915000000001</v>
+        <v>10.513915</v>
       </c>
       <c r="F85">
-        <v>0.10469199999999999</v>
+        <v>0.104692</v>
       </c>
       <c r="G85">
-        <v>1.4494E-2</v>
+        <v>0.014494</v>
       </c>
       <c r="H85">
         <v>-1</v>
@@ -6465,25 +5878,25 @@
         <v>229463</v>
       </c>
       <c r="T85" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U85" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V85" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W85" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X85" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y85" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>262144</v>
       </c>
@@ -6491,19 +5904,19 @@
         <v>-1</v>
       </c>
       <c r="C86">
-        <v>47.779744999999998</v>
+        <v>47.779745</v>
       </c>
       <c r="D86">
         <v>-1</v>
       </c>
       <c r="E86">
-        <v>42.298867000000001</v>
+        <v>42.298867</v>
       </c>
       <c r="F86">
-        <v>0.26188299999999998</v>
+        <v>0.261883</v>
       </c>
       <c r="G86">
-        <v>3.2342999999999997E-2</v>
+        <v>0.032343</v>
       </c>
       <c r="H86">
         <v>-1</v>
@@ -6542,127 +5955,127 @@
         <v>457255</v>
       </c>
       <c r="T86" t="s">
+        <v>16</v>
+      </c>
+      <c r="U86" t="s">
+        <v>16</v>
+      </c>
+      <c r="V86" t="s">
+        <v>16</v>
+      </c>
+      <c r="W86" t="s">
+        <v>16</v>
+      </c>
+      <c r="X86" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" t="s">
         <v>8</v>
       </c>
-      <c r="U86" t="s">
-        <v>8</v>
-      </c>
-      <c r="V86" t="s">
-        <v>8</v>
-      </c>
-      <c r="W86" t="s">
-        <v>8</v>
-      </c>
-      <c r="X86" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y86" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>12</v>
+      </c>
+      <c r="H89" t="s">
+        <v>13</v>
+      </c>
+      <c r="I89" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" t="s">
+        <v>13</v>
+      </c>
+      <c r="K89" t="s">
+        <v>13</v>
+      </c>
+      <c r="L89" t="s">
+        <v>13</v>
+      </c>
+      <c r="M89" t="s">
+        <v>13</v>
+      </c>
+      <c r="N89" t="s">
+        <v>14</v>
+      </c>
+      <c r="O89" t="s">
+        <v>14</v>
+      </c>
+      <c r="P89" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>14</v>
+      </c>
+      <c r="R89" t="s">
+        <v>14</v>
+      </c>
+      <c r="S89" t="s">
+        <v>14</v>
+      </c>
+      <c r="T89" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>29</v>
-      </c>
-      <c r="B89" t="s">
-        <v>2</v>
-      </c>
-      <c r="C89" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" t="s">
-        <v>7</v>
-      </c>
-      <c r="H89" t="s">
-        <v>31</v>
-      </c>
-      <c r="I89" t="s">
-        <v>31</v>
-      </c>
-      <c r="J89" t="s">
-        <v>31</v>
-      </c>
-      <c r="K89" t="s">
-        <v>31</v>
-      </c>
-      <c r="L89" t="s">
-        <v>31</v>
-      </c>
-      <c r="M89" t="s">
-        <v>31</v>
-      </c>
-      <c r="N89" t="s">
-        <v>32</v>
-      </c>
-      <c r="O89" t="s">
-        <v>32</v>
-      </c>
-      <c r="P89" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>32</v>
-      </c>
-      <c r="R89" t="s">
-        <v>32</v>
-      </c>
-      <c r="S89" t="s">
-        <v>32</v>
-      </c>
-      <c r="T89" t="s">
-        <v>25</v>
-      </c>
       <c r="U89" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="V89" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="W89" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="X89" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Y89" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>1024</v>
       </c>
       <c r="B90">
-        <v>2.0739999999999999E-3</v>
+        <v>0.002074</v>
       </c>
       <c r="C90">
-        <v>7.8799999999999996E-4</v>
+        <v>0.000788</v>
       </c>
       <c r="D90">
-        <v>9.2999999999999997E-5</v>
+        <v>0.000093</v>
       </c>
       <c r="E90">
-        <v>6.7500000000000004E-4</v>
+        <v>0.000675</v>
       </c>
       <c r="F90">
-        <v>1.56E-4</v>
+        <v>0.000156</v>
       </c>
       <c r="G90">
-        <v>9.3999999999999994E-5</v>
+        <v>0.000094</v>
       </c>
       <c r="H90">
         <v>523776</v>
@@ -6701,45 +6114,45 @@
         <v>2362</v>
       </c>
       <c r="T90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X90" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y90" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2048</v>
       </c>
       <c r="B91">
-        <v>7.7089999999999997E-3</v>
+        <v>0.007709</v>
       </c>
       <c r="C91">
-        <v>2.9250000000000001E-3</v>
+        <v>0.002925</v>
       </c>
       <c r="D91">
-        <v>1.93E-4</v>
+        <v>0.000193</v>
       </c>
       <c r="E91">
-        <v>2.4629999999999999E-3</v>
+        <v>0.002463</v>
       </c>
       <c r="F91">
-        <v>3.77E-4</v>
+        <v>0.000377</v>
       </c>
       <c r="G91">
-        <v>1.8900000000000001E-4</v>
+        <v>0.000189</v>
       </c>
       <c r="H91">
         <v>2096128</v>
@@ -6778,45 +6191,45 @@
         <v>5021</v>
       </c>
       <c r="T91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X91" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y91" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>4096</v>
       </c>
       <c r="B92">
-        <v>3.0176000000000001E-2</v>
+        <v>0.030176</v>
       </c>
       <c r="C92">
-        <v>1.1809999999999999E-2</v>
+        <v>0.01181</v>
       </c>
       <c r="D92">
-        <v>3.7199999999999999E-4</v>
+        <v>0.000372</v>
       </c>
       <c r="E92">
-        <v>1.0375000000000001E-2</v>
+        <v>0.010375</v>
       </c>
       <c r="F92">
-        <v>9.4700000000000003E-4</v>
+        <v>0.000947</v>
       </c>
       <c r="G92">
-        <v>3.4400000000000001E-4</v>
+        <v>0.000344</v>
       </c>
       <c r="H92">
         <v>8386560</v>
@@ -6855,45 +6268,45 @@
         <v>10687</v>
       </c>
       <c r="T92" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U92" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V92" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W92" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X92" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y92" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>8192</v>
       </c>
       <c r="B93">
-        <v>0.13913700000000001</v>
+        <v>0.139137</v>
       </c>
       <c r="C93">
-        <v>4.6669000000000002E-2</v>
+        <v>0.046669</v>
       </c>
       <c r="D93">
-        <v>8.9599999999999999E-4</v>
+        <v>0.000896</v>
       </c>
       <c r="E93">
-        <v>4.1055000000000001E-2</v>
+        <v>0.041055</v>
       </c>
       <c r="F93">
-        <v>2.4359999999999998E-3</v>
+        <v>0.002436</v>
       </c>
       <c r="G93">
-        <v>7.5000000000000002E-4</v>
+        <v>0.00075</v>
       </c>
       <c r="H93">
         <v>33550336</v>
@@ -6932,25 +6345,25 @@
         <v>22514</v>
       </c>
       <c r="T93" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U93" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V93" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W93" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X93" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y93" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>16384</v>
       </c>
@@ -6961,16 +6374,16 @@
         <v>0.186775</v>
       </c>
       <c r="D94">
-        <v>1.841E-3</v>
+        <v>0.001841</v>
       </c>
       <c r="E94">
-        <v>0.16413700000000001</v>
+        <v>0.164137</v>
       </c>
       <c r="F94">
-        <v>6.0390000000000001E-3</v>
+        <v>0.006039</v>
       </c>
       <c r="G94">
-        <v>1.9840000000000001E-3</v>
+        <v>0.001984</v>
       </c>
       <c r="H94">
         <v>134209536</v>
@@ -7009,25 +6422,25 @@
         <v>43762</v>
       </c>
       <c r="T94" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U94" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V94" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W94" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X94" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y94" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>32768</v>
       </c>
@@ -7035,19 +6448,19 @@
         <v>-1</v>
       </c>
       <c r="C95">
-        <v>0.74887800000000004</v>
+        <v>0.748878</v>
       </c>
       <c r="D95">
         <v>-1</v>
       </c>
       <c r="E95">
-        <v>0.66754100000000005</v>
+        <v>0.667541</v>
       </c>
       <c r="F95">
-        <v>1.6202999999999999E-2</v>
+        <v>0.016203</v>
       </c>
       <c r="G95">
-        <v>3.192E-3</v>
+        <v>0.003192</v>
       </c>
       <c r="H95">
         <v>-1</v>
@@ -7086,25 +6499,25 @@
         <v>93326</v>
       </c>
       <c r="T95" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U95" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V95" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W95" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X95" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y95" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>65536</v>
       </c>
@@ -7112,19 +6525,19 @@
         <v>-1</v>
       </c>
       <c r="C96">
-        <v>2.9832960000000002</v>
+        <v>2.983296</v>
       </c>
       <c r="D96">
         <v>-1</v>
       </c>
       <c r="E96">
-        <v>2.6563180000000002</v>
+        <v>2.656318</v>
       </c>
       <c r="F96">
-        <v>4.2172000000000001E-2</v>
+        <v>0.042172</v>
       </c>
       <c r="G96">
-        <v>6.5750000000000001E-3</v>
+        <v>0.006575</v>
       </c>
       <c r="H96">
         <v>-1</v>
@@ -7163,25 +6576,25 @@
         <v>186418</v>
       </c>
       <c r="T96" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U96" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V96" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W96" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X96" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y96" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>131072</v>
       </c>
@@ -7189,7 +6602,7 @@
         <v>-1</v>
       </c>
       <c r="C97">
-        <v>11.938618999999999</v>
+        <v>11.938619</v>
       </c>
       <c r="D97">
         <v>-1</v>
@@ -7201,7 +6614,7 @@
         <v>0.100235</v>
       </c>
       <c r="G97">
-        <v>1.3224E-2</v>
+        <v>0.013224</v>
       </c>
       <c r="H97">
         <v>-1</v>
@@ -7240,25 +6653,25 @@
         <v>407912</v>
       </c>
       <c r="T97" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U97" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V97" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W97" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X97" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y97" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>262144</v>
       </c>
@@ -7266,19 +6679,19 @@
         <v>-1</v>
       </c>
       <c r="C98">
-        <v>47.816111999999997</v>
+        <v>47.816112</v>
       </c>
       <c r="D98">
         <v>-1</v>
       </c>
       <c r="E98">
-        <v>42.195411999999997</v>
+        <v>42.195412</v>
       </c>
       <c r="F98">
-        <v>0.31597199999999998</v>
+        <v>0.315972</v>
       </c>
       <c r="G98">
-        <v>2.9076999999999999E-2</v>
+        <v>0.029077</v>
       </c>
       <c r="H98">
         <v>-1</v>
@@ -7317,49 +6730,49 @@
         <v>775930</v>
       </c>
       <c r="T98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="U98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="W98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="X98" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Y98" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C100" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D100" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E100" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1024</v>
       </c>
       <c r="B101" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C101">
         <v>523776</v>
@@ -7368,15 +6781,15 @@
         <v>772935</v>
       </c>
       <c r="E101">
-        <v>3.1449999999999998E-3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.003145</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1024</v>
       </c>
       <c r="B102" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C102">
         <v>523776</v>
@@ -7385,15 +6798,15 @@
         <v>3051</v>
       </c>
       <c r="E102">
-        <v>1.3309999999999999E-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.001331</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1024</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C103">
         <v>11069</v>
@@ -7402,15 +6815,15 @@
         <v>10874</v>
       </c>
       <c r="E103">
-        <v>7.4999999999999993E-5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.000075</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1024</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C104">
         <v>258664</v>
@@ -7419,15 +6832,15 @@
         <v>259691</v>
       </c>
       <c r="E104">
-        <v>1.178E-3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.001178</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1024</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C105">
         <v>21771</v>
@@ -7436,15 +6849,15 @@
         <v>31489</v>
       </c>
       <c r="E105">
-        <v>1.6200000000000001E-4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.000162</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>1024</v>
       </c>
       <c r="B106" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C106">
         <v>3069</v>
@@ -7453,15 +6866,15 @@
         <v>1024</v>
       </c>
       <c r="E106">
-        <v>6.0000000000000002E-5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.00006</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2048</v>
       </c>
       <c r="B107" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C107">
         <v>2096128</v>
@@ -7470,15 +6883,15 @@
         <v>3120921</v>
       </c>
       <c r="E107">
-        <v>1.2919999999999999E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.01292</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2048</v>
       </c>
       <c r="B108" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C108">
         <v>2096128</v>
@@ -7487,15 +6900,15 @@
         <v>6096</v>
       </c>
       <c r="E108">
-        <v>5.3049999999999998E-3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.005305</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2048</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C109">
         <v>23986</v>
@@ -7504,15 +6917,15 @@
         <v>24624</v>
       </c>
       <c r="E109">
-        <v>1.45E-4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.000145</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2048</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C110">
         <v>1042351</v>
@@ -7521,15 +6934,15 @@
         <v>1044401</v>
       </c>
       <c r="E110">
-        <v>4.5269999999999998E-3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.004527</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2048</v>
       </c>
       <c r="B111" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C111">
         <v>49183</v>
@@ -7538,15 +6951,15 @@
         <v>70690</v>
       </c>
       <c r="E111">
-        <v>3.4499999999999998E-4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+        <v>0.000345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2048</v>
       </c>
       <c r="B112" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C112">
         <v>6141</v>
@@ -7555,15 +6968,15 @@
         <v>2048</v>
       </c>
       <c r="E112">
-        <v>1.02E-4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000102</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4096</v>
       </c>
       <c r="B113" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C113">
         <v>8386560</v>
@@ -7572,15 +6985,15 @@
         <v>12637878</v>
       </c>
       <c r="E113">
-        <v>5.1403999999999998E-2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.051404</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>4096</v>
       </c>
       <c r="B114" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C114">
         <v>8386560</v>
@@ -7589,15 +7002,15 @@
         <v>12249</v>
       </c>
       <c r="E114">
-        <v>2.2585999999999998E-2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.022586</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>4096</v>
       </c>
       <c r="B115" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C115">
         <v>55640</v>
@@ -7606,15 +7019,15 @@
         <v>54760</v>
       </c>
       <c r="E115">
-        <v>3.19E-4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000319</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>4096</v>
       </c>
       <c r="B116" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C116">
         <v>4216715</v>
@@ -7623,15 +7036,15 @@
         <v>4220816</v>
       </c>
       <c r="E116">
-        <v>1.746E-2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.01746</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>4096</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C117">
         <v>105258</v>
@@ -7640,15 +7053,15 @@
         <v>152368</v>
       </c>
       <c r="E117">
-        <v>7.94E-4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000794</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>4096</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C118">
         <v>12285</v>
@@ -7657,15 +7070,15 @@
         <v>4096</v>
       </c>
       <c r="E118">
-        <v>2.1499999999999999E-4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000215</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>8192</v>
       </c>
       <c r="B119" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C119">
         <v>33550336</v>
@@ -7677,12 +7090,12 @@
         <v>0.221082</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>8192</v>
       </c>
       <c r="B120" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C120">
         <v>33550336</v>
@@ -7691,15 +7104,15 @@
         <v>24522</v>
       </c>
       <c r="E120">
-        <v>8.6044999999999996E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.086045</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>8192</v>
       </c>
       <c r="B121" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C121">
         <v>120040</v>
@@ -7708,15 +7121,15 @@
         <v>121294</v>
       </c>
       <c r="E121">
-        <v>6.5399999999999996E-4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000654</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>8192</v>
       </c>
       <c r="B122" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C122">
         <v>16481376</v>
@@ -7725,15 +7138,15 @@
         <v>16489573</v>
       </c>
       <c r="E122">
-        <v>6.9459000000000007E-2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.069459</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>8192</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C123">
         <v>253171</v>
@@ -7742,15 +7155,15 @@
         <v>355460</v>
       </c>
       <c r="E123">
-        <v>1.848E-3</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.001848</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>8192</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C124">
         <v>24573</v>
@@ -7759,15 +7172,15 @@
         <v>8192</v>
       </c>
       <c r="E124">
-        <v>3.5500000000000001E-4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000355</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>16384</v>
       </c>
       <c r="B125" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C125">
         <v>134209536</v>
@@ -7776,15 +7189,15 @@
         <v>197370135</v>
       </c>
       <c r="E125">
-        <v>0.92578099999999997</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.925781</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>16384</v>
       </c>
       <c r="B126" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C126">
         <v>134209536</v>
@@ -7796,12 +7209,12 @@
         <v>0.346692</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>16384</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C127">
         <v>255531</v>
@@ -7810,15 +7223,15 @@
         <v>264539</v>
       </c>
       <c r="E127">
-        <v>1.2949999999999999E-3</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.001295</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>16384</v>
       </c>
       <c r="B128" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C128">
         <v>65806424</v>
@@ -7827,15 +7240,15 @@
         <v>65822811</v>
       </c>
       <c r="E128">
-        <v>0.27432200000000001</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.274322</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>16384</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C129">
         <v>672857</v>
@@ -7844,15 +7257,15 @@
         <v>893842</v>
       </c>
       <c r="E129">
-        <v>4.1770000000000002E-3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.004177</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>16384</v>
       </c>
       <c r="B130" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C130">
         <v>49149</v>
@@ -7861,15 +7274,15 @@
         <v>16384</v>
       </c>
       <c r="E130">
-        <v>7.3300000000000004E-4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.000733</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>32768</v>
       </c>
       <c r="B131" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C131">
         <v>536854528</v>
@@ -7878,15 +7291,15 @@
         <v>788565897</v>
       </c>
       <c r="E131">
-        <v>3.8637700000000001</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3.86377</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>32768</v>
       </c>
       <c r="B132" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C132">
         <v>536854528</v>
@@ -7898,12 +7311,12 @@
         <v>1.406895</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>32768</v>
       </c>
       <c r="B133" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C133">
         <v>589636</v>
@@ -7912,15 +7325,15 @@
         <v>578305</v>
       </c>
       <c r="E133">
-        <v>3.143E-3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.003143</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>32768</v>
       </c>
       <c r="B134" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C134">
         <v>262888057</v>
@@ -7932,12 +7345,12 @@
         <v>1.105834</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>32768</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C135">
         <v>1450822</v>
@@ -7946,15 +7359,15 @@
         <v>1925486</v>
       </c>
       <c r="E135">
-        <v>9.1509999999999994E-3</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.009151</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>32768</v>
       </c>
       <c r="B136" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C136">
         <v>98301</v>
@@ -7963,15 +7376,15 @@
         <v>32768</v>
       </c>
       <c r="E136">
-        <v>1.3060000000000001E-3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.001306</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>65536</v>
       </c>
       <c r="B137" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C137">
         <v>2147450880</v>
@@ -7983,12 +7396,12 @@
         <v>15.777823</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>65536</v>
       </c>
       <c r="B138" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C138">
         <v>2147450880</v>
@@ -7997,15 +7410,15 @@
         <v>196575</v>
       </c>
       <c r="E138">
-        <v>5.5870110000000004</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5.587011</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>65536</v>
       </c>
       <c r="B139" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C139">
         <v>1233543</v>
@@ -8014,15 +7427,15 @@
         <v>1250633</v>
       </c>
       <c r="E139">
-        <v>6.9779999999999998E-3</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.006978</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>65536</v>
       </c>
       <c r="B140" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C140">
         <v>1051512198</v>
@@ -8031,15 +7444,15 @@
         <v>1051577743</v>
       </c>
       <c r="E140">
-        <v>4.4315550000000004</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4.431555</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>65536</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C141">
         <v>2827466</v>
@@ -8048,15 +7461,15 @@
         <v>3842308</v>
       </c>
       <c r="E141">
-        <v>1.8612E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.018612</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>65536</v>
       </c>
       <c r="B142" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C142">
         <v>196605</v>
@@ -8065,67 +7478,95 @@
         <v>65536</v>
       </c>
       <c r="E142">
-        <v>2.8999999999999998E-3</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.0029</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="2"/>
       <c r="B144" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="B145" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145" t="s">
+        <v>31</v>
+      </c>
+      <c r="D145" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="B146">
+        <v>0.000332</v>
+      </c>
+      <c r="C146">
+        <v>32640</v>
+      </c>
+      <c r="D146">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="B147">
+        <v>0.000099</v>
+      </c>
+      <c r="C147">
+        <v>32640</v>
+      </c>
+      <c r="D147">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>35</v>
+      </c>
+      <c r="B148">
+        <v>0.000111</v>
+      </c>
+      <c r="C148">
+        <v>32640</v>
+      </c>
+      <c r="D148">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A157" s="1">
-        <v>0.93902777777777779</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B149">
+        <v>0.000107</v>
+      </c>
+      <c r="C149">
+        <v>32640</v>
+      </c>
+      <c r="D149">
+        <v>46752</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>